--- a/reports/集团总公司_利润表_2025-10.xlsx
+++ b/reports/集团总公司_利润表_2025-10.xlsx
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>230908280</v>
+        <v>250466563</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>175798849</v>
+        <v>189591744</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>1694576033</v>
+        <v>1838378332</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>713987</v>
+        <v>926583</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>6910923</v>
+        <v>8940592</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>616957</v>
+        <v>811624</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>5994344</v>
+        <v>7825778</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>524405</v>
+        <v>685402</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>5078577</v>
+        <v>6608040</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>480109</v>
+        <v>632459</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>4671069</v>
+        <v>6100825</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>262255</v>
+        <v>347468</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>2538262</v>
+        <v>3355586</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>209077</v>
+        <v>273367</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>2030577</v>
+        <v>2643543</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>228101490</v>
+        <v>246789660</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>172992059</v>
+        <v>185914841</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>88988537</v>
+        <v>96946623</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>858336517</v>
+        <v>940155450</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1634496</v>
+        <v>2877154</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>15751511</v>
+        <v>27924332</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1472578</v>
+        <v>2091986</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>14229681</v>
+        <v>20304570</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>79155043</v>
+        <v>82665186</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>762050621</v>
+        <v>801741036</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1674584</v>
+        <v>2097680</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>16260675</v>
+        <v>20303761</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>738369</v>
+        <v>1050884</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>7115391</v>
+        <v>10155465</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2613906</v>
+        <v>3159269</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>25404664</v>
+        <v>30476269</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1155832</v>
+        <v>1580116</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>11178484</v>
+        <v>15241781</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>54939909</v>
+        <v>55123151</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>531388732</v>
+        <v>531947443</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>169522</v>
+        <v>170582</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>1699615</v>
+        <v>1701455</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>3350398</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>32335555</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>2230688</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>21556318</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>166662168</v>
+        <v>188085840</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>133880531</v>
+        <v>140662489</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>105520625</v>
+        <v>112334562</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>1017193557</v>
+        <v>1089491057</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>28359906</v>
+        <v>28327927</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>275342779</v>
+        <v>275034883</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>5541599</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>53814293</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1774026</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>17217629</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>1109958</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>10760690</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>1334022</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>12914313</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>1002278</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>9688065</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>669293</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>6460801</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>558447</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>5385884</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>3105255</v>
+        <v>3110069</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>29970665</v>
+        <v>29991027</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1451166</v>
+        <v>1466932</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>14118200</v>
+        <v>14131815</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>3785012</v>
+        <v>3782429</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>36568973</v>
+        <v>36601199</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>24420535</v>
+        <v>24444156</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>236682670</v>
+        <v>236832931</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>349578</v>
+        <v>2979646</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>3497459</v>
+        <v>28949782</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>1121257</v>
+        <v>1117428</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>11196899</v>
+        <v>11200657</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>1157814</v>
+        <v>1067858</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>11597582</v>
+        <v>10700016</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>120516</v>
+        <v>119538</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>1200015</v>
+        <v>1199507</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>474999</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>4766409</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>970274</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>9415773</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>317189</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>3177201</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>238272</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>2383302</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>397822</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>3973347</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1394634</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>13460623</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>212769</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>2120699</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>159665</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>1591027</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>266059</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>2652255</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>186078</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>1856682</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>132723</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>1326062</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>105995</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>1060590</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>79360</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>795170</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>61439322</v>
+        <v>62076429</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>66189790</v>
+        <v>65875392</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>554180</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>5381119</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>132027</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>1323803</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>210967</v>
+        <v>209505</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>2101046</v>
+        <v>2098185</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>61228355</v>
+        <v>62421104</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>7129674</v>
+        <v>7105924</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>71030478</v>
+        <v>70970170</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>54098681</v>
+        <v>55315180</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>54098681</v>
+        <v>55315180</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>54098681</v>
+        <v>55315180</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>54098681</v>
+        <v>55315180</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>54098681</v>
+        <v>55315180</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
